--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>10.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="R77" t="n">
-        <v>1.33</v>
+        <v>3.68</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.42</v>
+        <v>3.76</v>
       </c>
       <c r="R87" t="n">
-        <v>5.2</v>
+        <v>2.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,16 +17591,16 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R90" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R91" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,16 +18379,16 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R103" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R104" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,16 +20940,16 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R40" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.31</v>
+        <v>3.53</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="R51" t="n">
-        <v>3.15</v>
+        <v>1.96</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.7</v>
+        <v>4.04</v>
       </c>
       <c r="R86" t="n">
-        <v>3.68</v>
+        <v>4.99</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="R92" t="n">
-        <v>4.99</v>
+        <v>2.91</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R103" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R104" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,16 +20940,16 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,79 +10257,79 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10371,19 +10371,19 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.58</v>
+        <v>4.04</v>
       </c>
       <c r="R89" t="n">
-        <v>3</v>
+        <v>4.99</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="R90" t="n">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.42</v>
+        <v>3.58</v>
       </c>
       <c r="R91" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,16 +18379,16 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R92" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH92" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF92" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R103" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R104" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,16 +20940,16 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI104"/>
+  <dimension ref="A1:BI103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R42" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,79 +10257,79 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10371,19 +10371,19 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R75" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>10.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="R76" t="n">
-        <v>1.33</v>
+        <v>3.68</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="R87" t="n">
-        <v>4.11</v>
+        <v>3</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.04</v>
+        <v>4.42</v>
       </c>
       <c r="R89" t="n">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,16 +17985,16 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="R90" t="n">
-        <v>2.91</v>
+        <v>4.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18582,10 +18582,10 @@
         <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19069,27 +19069,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46134.875</v>
+        <v>46134.89583333334</v>
       </c>
     </row>
     <row r="96">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46134.89583333334</v>
+        <v>46134.9375</v>
       </c>
     </row>
     <row r="100">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46134.9375</v>
+        <v>46134.95833333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20552,10 +20552,10 @@
         <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46134.95833333334</v>
+        <v>46134.97916666666</v>
       </c>
     </row>
     <row r="103">
@@ -20833,203 +20833,6 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46134.97916666666</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P104" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="R104" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH104" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI104" s="3" t="n">
         <v>46134.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R39" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="R61" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>4.11</v>
+        <v>3.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.7</v>
+        <v>4.04</v>
       </c>
       <c r="R88" t="n">
-        <v>3.68</v>
+        <v>4.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="R90" t="n">
-        <v>4.99</v>
+        <v>2.91</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="R91" t="n">
-        <v>2.91</v>
+        <v>4.11</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R102" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,16 +20546,16 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R103" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R42" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.53</v>
+        <v>1.18</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.58</v>
+        <v>6.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.96</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R54" t="n">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R57" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.7</v>
+        <v>3.88</v>
       </c>
       <c r="R61" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R71" t="n">
-        <v>1.77</v>
+        <v>4.09</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="R72" t="n">
-        <v>17</v>
+        <v>4.69</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R74" t="n">
-        <v>4.09</v>
+        <v>1.77</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>10.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="R75" t="n">
-        <v>1.33</v>
+        <v>3.68</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R76" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="R88" t="n">
-        <v>4.99</v>
+        <v>2.91</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="R89" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,16 +17985,16 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R90" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,16 +18182,16 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH90" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>4.11</v>
+        <v>3.68</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q98" t="n">
         <v>3.74</v>
       </c>
       <c r="R98" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R71" t="n">
-        <v>4.09</v>
+        <v>4.69</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="R72" t="n">
-        <v>4.69</v>
+        <v>17</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="R73" t="n">
-        <v>17</v>
+        <v>4.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R76" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R77" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="R88" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="R89" t="n">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,55 +18334,55 @@
         </is>
       </c>
       <c r="P91" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF91" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R91" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>1.87</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.58</v>
+        <v>4.42</v>
       </c>
       <c r="R92" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R102" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,16 +20546,16 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R103" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.18</v>
+        <v>2.31</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.5</v>
+        <v>3.15</v>
       </c>
       <c r="R52" t="n">
-        <v>11</v>
+        <v>3.15</v>
       </c>
       <c r="S52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="R70" t="n">
-        <v>1.77</v>
+        <v>17</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R71" t="n">
-        <v>4.69</v>
+        <v>4.09</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R76" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R77" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>4.99</v>
+        <v>3.68</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R89" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,16 +17985,16 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH89" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="R91" t="n">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="R92" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R102" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,16 +20546,16 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R103" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R40" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R54" t="n">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R72" t="n">
-        <v>1.77</v>
+        <v>4.69</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="R74" t="n">
-        <v>4.69</v>
+        <v>17</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R76" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R77" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R87" t="n">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R88" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.42</v>
+        <v>3.58</v>
       </c>
       <c r="R89" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,16 +17985,16 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>2.91</v>
+        <v>3.68</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R92" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q97" t="n">
         <v>3.74</v>
       </c>
       <c r="R97" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.53</v>
+        <v>2.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R59" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="R64" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R72" t="n">
-        <v>4.69</v>
+        <v>4.09</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R73" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="R74" t="n">
-        <v>17</v>
+        <v>4.69</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R75" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>10.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="R77" t="n">
-        <v>1.33</v>
+        <v>3.68</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R88" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,16 +17788,16 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.58</v>
+        <v>4.04</v>
       </c>
       <c r="R89" t="n">
-        <v>3</v>
+        <v>4.99</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="R90" t="n">
-        <v>4.99</v>
+        <v>4.11</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.42</v>
+        <v>3.76</v>
       </c>
       <c r="R92" t="n">
-        <v>5.2</v>
+        <v>2.91</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R39" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R64" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="R65" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R67" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R68" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.47</v>
+        <v>4.55</v>
       </c>
       <c r="R69" t="n">
-        <v>10.5</v>
+        <v>6.82</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R73" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.58</v>
+        <v>4.04</v>
       </c>
       <c r="R86" t="n">
-        <v>3</v>
+        <v>4.99</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="R88" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,16 +17788,16 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="R89" t="n">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="R90" t="n">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R92" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH92" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF92" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R102" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,16 +20546,16 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R103" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R40" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R42" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R65" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>6.82</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R68" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.55</v>
+        <v>6.47</v>
       </c>
       <c r="R69" t="n">
-        <v>6.82</v>
+        <v>10.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.12</v>
+        <v>1.68</v>
       </c>
       <c r="Q71" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="R71" t="n">
-        <v>17</v>
+        <v>4.69</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R72" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R74" t="n">
-        <v>4.69</v>
+        <v>4.09</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R76" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.66</v>
+        <v>6.9</v>
       </c>
       <c r="R77" t="n">
-        <v>3.68</v>
+        <v>14</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.04</v>
+        <v>4.42</v>
       </c>
       <c r="R86" t="n">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R87" t="n">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R89" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="R90" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,61 +18531,61 @@
         </is>
       </c>
       <c r="P92" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q92" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R92" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="n">
-        <v>0</v>
-      </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q98" t="n">
         <v>3.74</v>
       </c>
       <c r="R98" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R102" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,16 +20546,16 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R103" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,16 +20743,16 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.18</v>
+        <v>2.31</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.5</v>
+        <v>3.15</v>
       </c>
       <c r="R47" t="n">
-        <v>11</v>
+        <v>3.15</v>
       </c>
       <c r="S47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10174,19 +10174,19 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.7</v>
+        <v>3.88</v>
       </c>
       <c r="R65" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.55</v>
+        <v>6.47</v>
       </c>
       <c r="R67" t="n">
-        <v>6.82</v>
+        <v>10.5</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="R68" t="n">
-        <v>2.42</v>
+        <v>6.82</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R69" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.68</v>
+        <v>4.3</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>4.69</v>
+        <v>1.77</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="R72" t="n">
-        <v>17</v>
+        <v>4.09</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R74" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.66</v>
+        <v>6.9</v>
       </c>
       <c r="R76" t="n">
-        <v>3.68</v>
+        <v>14</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R77" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="R86" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="R87" t="n">
-        <v>2.91</v>
+        <v>4.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R89" t="n">
-        <v>4.11</v>
+        <v>3.68</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.58</v>
+        <v>4.42</v>
       </c>
       <c r="R90" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,16 +18182,16 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R91" t="n">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="R92" t="n">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q96" t="n">
         <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R39" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.53</v>
+        <v>2.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="R46" t="n">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10174,19 +10174,19 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R57" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R67" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.55</v>
+        <v>6.47</v>
       </c>
       <c r="R68" t="n">
-        <v>6.82</v>
+        <v>10.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="R69" t="n">
-        <v>2.42</v>
+        <v>6.82</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>4.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R71" t="n">
-        <v>1.77</v>
+        <v>4.09</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>4.09</v>
+        <v>1.77</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R86" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="R87" t="n">
-        <v>4.99</v>
+        <v>4.11</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R89" t="n">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="R91" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="R92" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q96" t="n">
         <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q97" t="n">
         <v>3.74</v>
       </c>
       <c r="R97" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11687,10 +11687,10 @@
         <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="R60" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R62" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R68" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R71" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R72" t="n">
-        <v>1.77</v>
+        <v>4.09</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R74" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R75" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R76" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.42</v>
+        <v>3.58</v>
       </c>
       <c r="R86" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
       <c r="R87" t="n">
-        <v>4.11</v>
+        <v>4.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="R88" t="n">
-        <v>4.99</v>
+        <v>4.11</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R89" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,16 +17985,16 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH89" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF89" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="n">
-        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R92" t="n">
-        <v>3.68</v>
+        <v>2.91</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q96" t="n">
         <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R40" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.47</v>
+        <v>4.55</v>
       </c>
       <c r="R67" t="n">
-        <v>10.5</v>
+        <v>6.82</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R68" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R69" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q71" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="R71" t="n">
-        <v>17</v>
+        <v>4.09</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R72" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.68</v>
+        <v>4.3</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R73" t="n">
-        <v>4.69</v>
+        <v>1.77</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>4.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R74" t="n">
-        <v>1.77</v>
+        <v>4.69</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R75" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R76" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R86" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>4.99</v>
+        <v>3.68</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="R88" t="n">
-        <v>4.11</v>
+        <v>3</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,61 +17940,61 @@
         </is>
       </c>
       <c r="P89" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R89" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q89" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R89" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="n">
-        <v>0</v>
-      </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.7</v>
+        <v>4.42</v>
       </c>
       <c r="R90" t="n">
-        <v>3.68</v>
+        <v>5.2</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,16 +18182,16 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q96" t="n">
         <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>2.81</v>
+        <v>4.38</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R39" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R41" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="R59" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R64" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R68" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R69" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R71" t="n">
-        <v>4.09</v>
+        <v>4.69</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q72" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="R73" t="n">
-        <v>1.77</v>
+        <v>17</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R74" t="n">
-        <v>4.69</v>
+        <v>4.09</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R86" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.04</v>
+        <v>3.76</v>
       </c>
       <c r="R89" t="n">
-        <v>4.99</v>
+        <v>2.91</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.42</v>
+        <v>3.7</v>
       </c>
       <c r="R90" t="n">
-        <v>5.2</v>
+        <v>3.68</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,16 +18182,16 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="R92" t="n">
-        <v>2.91</v>
+        <v>4.11</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI103"/>
+  <dimension ref="A1:BI102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10765,19 +10765,19 @@
         <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46134.61458333334</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="59">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.63541666666</v>
       </c>
     </row>
     <row r="66">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46134.63541666666</v>
+        <v>46134.64583333334</v>
       </c>
     </row>
     <row r="67">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R67" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R68" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.47</v>
+        <v>3.65</v>
       </c>
       <c r="R69" t="n">
-        <v>10.5</v>
+        <v>4.09</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46134.64583333334</v>
+        <v>46134.65625</v>
       </c>
     </row>
     <row r="70">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>8</v>
+        <v>1.77</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="R71" t="n">
-        <v>4.69</v>
+        <v>8</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R72" t="n">
-        <v>1.77</v>
+        <v>4.69</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.81</v>
+        <v>10.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.65</v>
+        <v>5.98</v>
       </c>
       <c r="R74" t="n">
-        <v>4.09</v>
+        <v>1.33</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46134.65625</v>
+        <v>46134.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R75" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R76" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15523,12 +15523,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46134.66666666666</v>
+        <v>46134.6875</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46134.6875</v>
+        <v>46134.72916666666</v>
       </c>
     </row>
     <row r="79">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16508,27 +16508,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46134.72916666666</v>
+        <v>46134.79166666666</v>
       </c>
     </row>
     <row r="83">
@@ -16902,27 +16902,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46134.79166666666</v>
+        <v>46134.83333333334</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46134.83333333334</v>
+        <v>46134.85416666666</v>
       </c>
     </row>
     <row r="86">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="R86" t="n">
-        <v>5.2</v>
+        <v>4.11</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="R88" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.7</v>
+        <v>4.42</v>
       </c>
       <c r="R90" t="n">
-        <v>3.68</v>
+        <v>5.2</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,16 +18182,16 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="R91" t="n">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.875</v>
       </c>
     </row>
     <row r="93">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="R94" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,16 +18970,16 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46134.875</v>
+        <v>46134.89583333334</v>
       </c>
     </row>
     <row r="95">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="R98" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,16 +19758,16 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46134.89583333334</v>
+        <v>46134.9375</v>
       </c>
     </row>
     <row r="99">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20158,10 +20158,10 @@
         <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46134.9375</v>
+        <v>46134.95833333334</v>
       </c>
     </row>
     <row r="101">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46134.95833333334</v>
+        <v>46134.97916666666</v>
       </c>
     </row>
     <row r="102">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R102" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,16 +20546,16 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20636,203 +20636,6 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46134.97916666666</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P103" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="R103" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG103" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH103" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH103" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI103" s="3" t="n">
         <v>46134.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI102"/>
+  <dimension ref="A1:BI106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46134.4375</v>
+        <v>46134.41666666666</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46134.45833333334</v>
+        <v>46134.4375</v>
       </c>
     </row>
     <row r="16">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46134.47916666666</v>
+        <v>46134.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46134.47916666666</v>
+        <v>46134.45833333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46134.47916666666</v>
+        <v>46134.45833333334</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46134.5</v>
+        <v>46134.45833333334</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46134.5</v>
+        <v>46134.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46134.5</v>
+        <v>46134.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46134.5</v>
+        <v>46134.47916666666</v>
       </c>
     </row>
     <row r="26">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46134.51041666666</v>
+        <v>46134.47916666666</v>
       </c>
     </row>
     <row r="27">
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46134.53125</v>
+        <v>46134.47916666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46134.53125</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,28 +6317,28 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="33">
@@ -6855,27 +6855,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6917,13 +6917,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.5</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.51041666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.53125</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46134.54166666666</v>
+        <v>46134.53125</v>
       </c>
     </row>
     <row r="37">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46134.5625</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>5.13</v>
+        <v>4.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46134.5625</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46134.57291666666</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="42">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>4.82</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46134.57291666666</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>5.14</v>
+        <v>2.81</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46134.57291666666</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.54166666666</v>
       </c>
     </row>
     <row r="47">
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9705,40 +9705,40 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.5625</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.5625</v>
       </c>
     </row>
     <row r="49">
@@ -10007,27 +10007,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.5625</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.57291666666</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.99</v>
       </c>
       <c r="R51" t="n">
-        <v>3.15</v>
+        <v>5.14</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.57291666666</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46134.58333333334</v>
+        <v>46134.57291666666</v>
       </c>
     </row>
     <row r="53">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,79 +10848,79 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
@@ -10962,19 +10962,19 @@
         <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46134.60416666666</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46134.60416666666</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46134.60416666666</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46134.60416666666</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,79 +12227,79 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO60" t="n">
         <v>0</v>
@@ -12341,19 +12341,19 @@
         <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.86</v>
+        <v>3.53</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="R61" t="n">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.88</v>
+        <v>3.15</v>
       </c>
       <c r="R62" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46134.625</v>
+        <v>46134.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46134.63541666666</v>
+        <v>46134.60416666666</v>
       </c>
     </row>
     <row r="66">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46134.64583333334</v>
+        <v>46134.60416666666</v>
       </c>
     </row>
     <row r="67">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46134.64583333334</v>
+        <v>46134.60416666666</v>
       </c>
     </row>
     <row r="68">
@@ -13750,27 +13750,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46134.64583333334</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="69">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>4.09</v>
+        <v>2.81</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46134.65625</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="R70" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46134.65625</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46134.65625</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46134.65625</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="73">
@@ -14735,27 +14735,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46134.65625</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>10.4</v>
+        <v>2.86</v>
       </c>
       <c r="Q74" t="n">
-        <v>5.98</v>
+        <v>2.7</v>
       </c>
       <c r="R74" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46134.66666666666</v>
+        <v>46134.625</v>
       </c>
     </row>
     <row r="75">
@@ -15129,27 +15129,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46134.66666666666</v>
+        <v>46134.63541666666</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.13</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.66</v>
+        <v>4.55</v>
       </c>
       <c r="R76" t="n">
-        <v>3.68</v>
+        <v>6.82</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46134.66666666666</v>
+        <v>46134.64583333334</v>
       </c>
     </row>
     <row r="77">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46134.6875</v>
+        <v>46134.64583333334</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46134.72916666666</v>
+        <v>46134.64583333334</v>
       </c>
     </row>
     <row r="79">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46134.72916666666</v>
+        <v>46134.65625</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46134.72916666666</v>
+        <v>46134.65625</v>
       </c>
     </row>
     <row r="81">
@@ -16311,27 +16311,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46134.72916666666</v>
+        <v>46134.65625</v>
       </c>
     </row>
     <row r="82">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46134.79166666666</v>
+        <v>46134.65625</v>
       </c>
     </row>
     <row r="83">
@@ -16705,27 +16705,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>3.46</v>
+        <v>4.69</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46134.79166666666</v>
+        <v>46134.65625</v>
       </c>
     </row>
     <row r="84">
@@ -16902,27 +16902,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46134.83333333334</v>
+        <v>46134.66666666666</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.04</v>
+        <v>6.9</v>
       </c>
       <c r="R85" t="n">
-        <v>4.99</v>
+        <v>14</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.89</v>
+        <v>10.4</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.85</v>
+        <v>5.98</v>
       </c>
       <c r="R86" t="n">
-        <v>4.11</v>
+        <v>1.33</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.66666666666</v>
       </c>
     </row>
     <row r="87">
@@ -17493,27 +17493,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.6875</v>
       </c>
     </row>
     <row r="88">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.72916666666</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.79166666666</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46134.85416666666</v>
+        <v>46134.83333333334</v>
       </c>
     </row>
     <row r="91">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.58</v>
+        <v>4.42</v>
       </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,16 +18379,16 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46134.875</v>
+        <v>46134.85416666666</v>
       </c>
     </row>
     <row r="93">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="R93" t="n">
-        <v>3.78</v>
+        <v>4.11</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,16 +18773,16 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46134.875</v>
+        <v>46134.85416666666</v>
       </c>
     </row>
     <row r="94">
@@ -18872,7 +18872,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="R94" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46134.89583333334</v>
+        <v>46134.85416666666</v>
       </c>
     </row>
     <row r="95">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46134.89583333334</v>
+        <v>46134.85416666666</v>
       </c>
     </row>
     <row r="96">
@@ -19266,27 +19266,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46134.89583333334</v>
+        <v>46134.85416666666</v>
       </c>
     </row>
     <row r="97">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,133 +19516,133 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI97" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM97" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO97" t="n">
         <v>0</v>
       </c>
       <c r="AP97" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS97" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU97" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV97" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW97" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY97" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA97" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD97" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE97" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF97" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46134.89583333334</v>
+        <v>46134.86458333334</v>
       </c>
     </row>
     <row r="98">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="R98" t="n">
-        <v>2.64</v>
+        <v>3.78</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19764,10 +19764,10 @@
         <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46134.9375</v>
+        <v>46134.875</v>
       </c>
     </row>
     <row r="99">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46134.9375</v>
+        <v>46134.89583333334</v>
       </c>
     </row>
     <row r="100">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46134.95833333334</v>
+        <v>46134.89583333334</v>
       </c>
     </row>
     <row r="101">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.69</v>
+        <v>2.33</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.21</v>
+        <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46134.97916666666</v>
+        <v>46134.89583333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,141 +20501,929 @@
         </is>
       </c>
       <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI102" s="3" t="n">
+        <v>46134.91666666666</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R103" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI103" s="3" t="n">
+        <v>46134.9375</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI104" s="3" t="n">
+        <v>46134.95833333334</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
         <v>1.47</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="Q105" t="n">
         <v>4.89</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R105" t="n">
         <v>6.91</v>
       </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="n">
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
         <v>2.05</v>
       </c>
-      <c r="AH102" t="n">
+      <c r="AH105" t="n">
         <v>1.68</v>
       </c>
-      <c r="AI102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH102" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI102" s="3" t="n">
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI105" s="3" t="n">
+        <v>46134.97916666666</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="R106" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI106" s="3" t="n">
         <v>46134.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,28 +6120,28 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -6159,40 +6159,40 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,70 +6326,70 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="U30" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG30" t="n">
         <v>2.6</v>
       </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6917,13 +6917,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>4.82</v>
+        <v>2.81</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R51" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,79 +12227,79 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO60" t="n">
         <v>0</v>
@@ -12341,19 +12341,19 @@
         <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG60" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.31</v>
+        <v>1.18</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.15</v>
+        <v>6.5</v>
       </c>
       <c r="R62" t="n">
-        <v>3.15</v>
+        <v>11</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12735,19 +12735,19 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R65" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R69" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.88</v>
+        <v>2.7</v>
       </c>
       <c r="R70" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R76" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="R78" t="n">
-        <v>2.42</v>
+        <v>6.82</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q79" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="R80" t="n">
-        <v>8</v>
+        <v>4.69</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R81" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="R82" t="n">
-        <v>1.77</v>
+        <v>8</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R83" t="n">
-        <v>4.69</v>
+        <v>4.09</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R84" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R85" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R86" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.42</v>
+        <v>3.58</v>
       </c>
       <c r="R91" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,16 +18379,16 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="R92" t="n">
-        <v>2.91</v>
+        <v>4.11</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R93" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,16 +18773,16 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q99" t="n">
         <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q101" t="n">
         <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5932,13 +5932,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5947,10 +5947,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6129,19 +6129,19 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -6159,40 +6159,40 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,22 +6317,22 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6917,19 +6917,19 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9705,40 +9705,40 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9902,40 +9902,40 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R51" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.53</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="R61" t="n">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.18</v>
+        <v>2.88</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="R62" t="n">
-        <v>11</v>
+        <v>2.32</v>
       </c>
       <c r="S62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z62" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF62" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12735,19 +12735,19 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,79 +12818,79 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.31</v>
+        <v>1.18</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.15</v>
+        <v>6.5</v>
       </c>
       <c r="R63" t="n">
-        <v>3.15</v>
+        <v>11</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
@@ -12932,19 +12932,19 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC63" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD63" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R68" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R71" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R76" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.47</v>
+        <v>4.55</v>
       </c>
       <c r="R77" t="n">
-        <v>10.5</v>
+        <v>6.82</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R78" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q81" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="R81" t="n">
-        <v>17</v>
+        <v>4.09</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="R82" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="R83" t="n">
-        <v>4.09</v>
+        <v>8</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R84" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R85" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R86" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,61 +18728,61 @@
         </is>
       </c>
       <c r="P93" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R93" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q93" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R93" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>0</v>
-      </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="R95" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.04</v>
+        <v>4.42</v>
       </c>
       <c r="R96" t="n">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,16 +19364,16 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5932,13 +5932,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5947,10 +5947,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,19 +6720,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6917,70 +6917,70 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T33" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG33" t="n">
         <v>2.6</v>
       </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>4.38</v>
+        <v>2.81</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>2.81</v>
+        <v>4.82</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R47" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9902,40 +9902,40 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10099,40 +10099,40 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>3.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="R51" t="n">
-        <v>5.14</v>
+        <v>2.06</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R52" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,79 +11439,79 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
@@ -11553,19 +11553,19 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="R62" t="n">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,79 +12818,79 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.18</v>
+        <v>2.88</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="R63" t="n">
-        <v>11</v>
+        <v>2.32</v>
       </c>
       <c r="S63" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z63" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF63" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
@@ -12932,19 +12932,19 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R66" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q84" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R84" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.66</v>
+        <v>6.9</v>
       </c>
       <c r="R86" t="n">
-        <v>3.68</v>
+        <v>14</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R91" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,16 +18379,16 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH91" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="n">
-        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
       <c r="R92" t="n">
-        <v>4.11</v>
+        <v>4.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="R93" t="n">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R95" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19370,10 +19370,10 @@
         <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q99" t="n">
         <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q101" t="n">
         <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,19 +6720,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6917,13 +6917,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>4.38</v>
+        <v>2.81</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q46" t="n">
         <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>4.82</v>
+        <v>4.38</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10099,40 +10099,40 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="R51" t="n">
-        <v>2.06</v>
+        <v>5.14</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.43</v>
+        <v>3.53</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="R54" t="n">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R66" t="n">
-        <v>3.7</v>
+        <v>8.25</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R70" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R71" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.47</v>
+        <v>4.55</v>
       </c>
       <c r="R76" t="n">
-        <v>10.5</v>
+        <v>6.82</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R77" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R78" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R79" t="n">
-        <v>1.77</v>
+        <v>4.09</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.68</v>
+        <v>4.3</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R80" t="n">
-        <v>4.69</v>
+        <v>1.77</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="R81" t="n">
-        <v>4.09</v>
+        <v>8</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>8</v>
+        <v>4.69</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.66</v>
+        <v>6.9</v>
       </c>
       <c r="R84" t="n">
-        <v>3.68</v>
+        <v>14</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R86" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="R94" t="n">
-        <v>2.91</v>
+        <v>4.99</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="R95" t="n">
-        <v>4.11</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q99" t="n">
         <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R105" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,16 +21137,16 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R106" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,16 +21334,16 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.72</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.59</v>
+        <v>4.82</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>4.72</v>
       </c>
       <c r="Q42" t="n">
         <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>4.82</v>
+        <v>1.59</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R47" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,79 +11439,79 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
@@ -11553,19 +11553,19 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12735,19 +12735,19 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.55</v>
+        <v>6.47</v>
       </c>
       <c r="R76" t="n">
-        <v>6.82</v>
+        <v>10.5</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="R77" t="n">
-        <v>2.42</v>
+        <v>6.82</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R78" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>4.09</v>
+        <v>1.77</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="R80" t="n">
-        <v>1.77</v>
+        <v>17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="R81" t="n">
-        <v>8</v>
+        <v>4.09</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="Q82" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="R82" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>10.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="R85" t="n">
-        <v>1.33</v>
+        <v>3.68</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R86" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="R93" t="n">
-        <v>4.11</v>
+        <v>3</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="R94" t="n">
-        <v>4.99</v>
+        <v>4.11</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.58</v>
+        <v>4.04</v>
       </c>
       <c r="R95" t="n">
-        <v>3</v>
+        <v>4.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.76</v>
+        <v>4.42</v>
       </c>
       <c r="R96" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,16 +19364,16 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH96" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>4.72</v>
       </c>
       <c r="Q39" t="n">
         <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>4.38</v>
+        <v>1.59</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.72</v>
+        <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.59</v>
+        <v>2.81</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>4.84</v>
+        <v>5.13</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R49" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,79 +11242,79 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11356,19 +11356,19 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.53</v>
+        <v>2.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>1.96</v>
+        <v>3.15</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>1.43</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R60" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12735,19 +12735,19 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.43</v>
+        <v>2.88</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R63" t="n">
-        <v>6.6</v>
+        <v>2.32</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R64" t="n">
-        <v>3.7</v>
+        <v>8.25</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13066,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R66" t="n">
-        <v>8.25</v>
+        <v>4.09</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.47</v>
+        <v>4.55</v>
       </c>
       <c r="R76" t="n">
-        <v>10.5</v>
+        <v>6.82</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.55</v>
+        <v>6.47</v>
       </c>
       <c r="R77" t="n">
-        <v>6.82</v>
+        <v>10.5</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R79" t="n">
-        <v>1.77</v>
+        <v>4.09</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R81" t="n">
-        <v>4.09</v>
+        <v>1.77</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="R82" t="n">
-        <v>8</v>
+        <v>4.69</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="R83" t="n">
-        <v>4.69</v>
+        <v>8</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q84" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R84" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.66</v>
+        <v>6.9</v>
       </c>
       <c r="R85" t="n">
-        <v>3.68</v>
+        <v>14</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>10.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.98</v>
+        <v>3.66</v>
       </c>
       <c r="R86" t="n">
-        <v>1.33</v>
+        <v>3.68</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.89</v>
+        <v>2.39</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="R94" t="n">
-        <v>4.11</v>
+        <v>3</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="R95" t="n">
-        <v>4.99</v>
+        <v>4.11</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,61 +19319,61 @@
         </is>
       </c>
       <c r="P96" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R96" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q96" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R96" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>0</v>
-      </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.72</v>
+        <v>2.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.59</v>
+        <v>2.81</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R47" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,79 +11242,79 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11356,19 +11356,19 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,79 +11636,79 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.31</v>
+        <v>1.18</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.15</v>
+        <v>6.5</v>
       </c>
       <c r="R57" t="n">
-        <v>3.15</v>
+        <v>11</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11750,19 +11750,19 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R66" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="R73" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="R74" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="R76" t="n">
-        <v>6.82</v>
+        <v>2.42</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>6.47</v>
+        <v>4.55</v>
       </c>
       <c r="R77" t="n">
-        <v>10.5</v>
+        <v>6.82</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R78" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="R79" t="n">
-        <v>4.09</v>
+        <v>8</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q80" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="R80" t="n">
-        <v>17</v>
+        <v>4.09</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="R81" t="n">
-        <v>1.77</v>
+        <v>17</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R83" t="n">
-        <v>8</v>
+        <v>1.77</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q85" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R85" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.66</v>
+        <v>6.9</v>
       </c>
       <c r="R86" t="n">
-        <v>3.68</v>
+        <v>14</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.76</v>
+        <v>4.04</v>
       </c>
       <c r="R93" t="n">
-        <v>2.91</v>
+        <v>4.99</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="R95" t="n">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,16 +19167,16 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="R96" t="n">
-        <v>4.99</v>
+        <v>3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q99" t="n">
         <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R105" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,16 +21137,16 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R106" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,16 +21334,16 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.51</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>3.59</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>4.74</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.24</v>
+        <v>2.07</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,13 +6326,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6359,37 +6359,37 @@
         <v>1.19</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
         <v>2.04</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" t="n">
         <v>4.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6720,19 +6720,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>6.76</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.72</v>
+        <v>3.02</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="R37" t="n">
-        <v>1.59</v>
+        <v>2.69</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="R38" t="n">
-        <v>4.82</v>
+        <v>4.38</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.81</v>
+        <v>4.38</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="R41" t="n">
-        <v>4.38</v>
+        <v>7.21</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9705,40 +9705,40 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R48" t="n">
-        <v>5.13</v>
+        <v>4.84</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9944,52 +9944,52 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU48" t="n">
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10141,52 +10141,52 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU49" t="n">
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,79 +10454,79 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10568,19 +10568,19 @@
         <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY53" t="n">
         <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W57" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>1.18</v>
       </c>
-      <c r="Q57" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R57" t="n">
-        <v>11</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U57" t="n">
-        <v>8</v>
-      </c>
-      <c r="V57" t="n">
+      <c r="AK57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB57" t="n">
         <v>1.18</v>
       </c>
-      <c r="W57" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X57" t="n">
+      <c r="BC57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE57" t="n">
         <v>1.91</v>
       </c>
-      <c r="Y57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BF57" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.53</v>
+        <v>2.88</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="R58" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,79 +12030,79 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.43</v>
+        <v>3.53</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="R59" t="n">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO59" t="n">
         <v>0</v>
@@ -12144,19 +12144,19 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,133 +12621,133 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.88</v>
+        <v>1.18</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="R62" t="n">
-        <v>2.32</v>
+        <v>11</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AF62" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL62" t="n">
         <v>1.88</v>
       </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,133 +13212,133 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,79 +13409,79 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R66" t="n">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL66" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
@@ -13523,19 +13523,19 @@
         <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD66" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,79 +13606,79 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R67" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
@@ -13720,19 +13720,19 @@
         <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC67" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD67" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE67" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,133 +13803,133 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY68" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="R70" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R72" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R72" t="n">
-        <v>2.5</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,133 +14788,133 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R73" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO73" t="n">
         <v>0</v>
       </c>
       <c r="AP73" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR73" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV73" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AW73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX73" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AY73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA73" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB73" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD73" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE73" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF73" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,133 +14985,133 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.86</v>
+        <v>1.79</v>
       </c>
       <c r="Q74" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R74" t="n">
+        <v>5</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W74" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC74" t="n">
         <v>2.7</v>
       </c>
-      <c r="R74" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC74" t="n">
-        <v>0</v>
-      </c>
       <c r="BD74" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG74" t="n">
         <v>0</v>
@@ -15182,22 +15182,22 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -15206,37 +15206,37 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB75" t="n">
         <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15245,16 +15245,16 @@
         <v>0</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
@@ -15299,13 +15299,13 @@
         <v>0</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD75" t="n">
         <v>0</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,133 +15379,133 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.46</v>
+        <v>6.47</v>
       </c>
       <c r="R76" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR76" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AW76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA76" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB76" t="n">
         <v>0</v>
       </c>
       <c r="BC76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD76" t="n">
         <v>0</v>
       </c>
       <c r="BE76" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BF76" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15585,124 +15585,124 @@
         <v>6.82</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM77" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AO77" t="n">
         <v>0</v>
       </c>
       <c r="AP77" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS77" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX77" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ77" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA77" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB77" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD77" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF77" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,133 +15773,133 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R78" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL78" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO78" t="n">
         <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,133 +15970,133 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="R79" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR79" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS79" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="BB79" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BD79" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE79" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF79" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG79" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="R81" t="n">
-        <v>17</v>
+        <v>1.77</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R82" t="n">
+        <v>8</v>
+      </c>
+      <c r="S82" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="T82" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X82" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN82" t="n">
         <v>3.7</v>
       </c>
-      <c r="R82" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>0</v>
-      </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BB82" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>1.77</v>
+        <v>4.69</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R84" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.12</v>
+        <v>10.4</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="R86" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.42</v>
+        <v>3.76</v>
       </c>
       <c r="R95" t="n">
-        <v>5.2</v>
+        <v>2.91</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,16 +19167,16 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.39</v>
+        <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.58</v>
+        <v>4.42</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,16 +19364,16 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.89</v>
+        <v>4.21</v>
       </c>
       <c r="R105" t="n">
-        <v>6.91</v>
+        <v>4.99</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,16 +21137,16 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.21</v>
+        <v>4.89</v>
       </c>
       <c r="R106" t="n">
-        <v>4.99</v>
+        <v>6.91</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,16 +21334,16 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>3.71</v>
+        <v>3.03</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>4.65</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="X18" t="n">
         <v>3.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="AA18" t="n">
         <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF18" t="n">
         <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="R23" t="n">
-        <v>3.03</v>
+        <v>3.79</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U23" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="X23" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="AH23" t="n">
         <v>1.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.96</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>4.17</v>
+        <v>2.07</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
-        <v>3.24</v>
+        <v>4.17</v>
       </c>
       <c r="S26" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="R27" t="n">
-        <v>2.07</v>
+        <v>3.24</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="T27" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>2.51</v>
+        <v>4.45</v>
       </c>
       <c r="V27" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="X27" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.04</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK27" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,13 +6326,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6523,13 +6523,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6556,37 +6556,37 @@
         <v>1.19</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
         <v>2.04</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" t="n">
         <v>4.6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6631,13 +6631,13 @@
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>6.76</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.1</v>
+        <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="R36" t="n">
-        <v>2.1</v>
+        <v>6.76</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.02</v>
+        <v>4.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.91</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.69</v>
+        <v>1.59</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
         <v>4.38</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>4.38</v>
+        <v>2.81</v>
       </c>
       <c r="S39" t="n">
-        <v>2.15</v>
+        <v>2.84</v>
       </c>
       <c r="T39" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="U39" t="n">
-        <v>4.57</v>
+        <v>3.3</v>
       </c>
       <c r="V39" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W39" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="X39" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL39" t="n">
         <v>2.5</v>
       </c>
       <c r="AM39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
         <v>1.18</v>
       </c>
-      <c r="AN39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AQ39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="BA39" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.3</v>
+        <v>4.85</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R40" t="n">
-        <v>2.81</v>
+        <v>4.38</v>
       </c>
       <c r="S40" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>7.21</v>
+        <v>4.82</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.58</v>
+        <v>3.02</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="R45" t="n">
-        <v>4.82</v>
+        <v>2.69</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AE47" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR47" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF47" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU47" t="n">
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL49" t="n">
         <v>2.15</v>
       </c>
-      <c r="T49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W49" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AM49" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10141,52 +10141,52 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,79 +10257,79 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10371,19 +10371,19 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,79 +10454,79 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10568,19 +10568,19 @@
         <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY53" t="n">
         <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,79 +11242,79 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
@@ -11356,19 +11356,19 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T57" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="U57" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="V57" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W57" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y57" t="n">
         <v>1.29</v>
       </c>
-      <c r="W57" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="X57" t="n">
+      <c r="Z57" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC57" t="n">
         <v>2.44</v>
       </c>
-      <c r="Y57" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD57" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,133 +11833,133 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="Q58" t="n">
         <v>3.45</v>
       </c>
       <c r="R58" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W58" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF58" t="n">
         <v>2.32</v>
       </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
+      <c r="AG58" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW58" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF58" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0</v>
-      </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,79 +12030,79 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.53</v>
+        <v>1.43</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="R59" t="n">
-        <v>1.96</v>
+        <v>6.6</v>
       </c>
       <c r="S59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO59" t="n">
         <v>0</v>
@@ -12144,19 +12144,19 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,133 +12227,133 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO60" t="n">
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,133 +12621,133 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.18</v>
+        <v>2.88</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="R62" t="n">
-        <v>11</v>
+        <v>2.32</v>
       </c>
       <c r="S62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z62" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF62" t="n">
-        <v>2.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BA62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,79 +13015,79 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AO64" t="n">
         <v>0</v>
@@ -13129,19 +13129,19 @@
         <v>0</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,133 +13212,133 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W65" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z65" t="n">
         <v>4.2</v>
       </c>
-      <c r="R65" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U65" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W65" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Y65" t="n">
+      <c r="AA65" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BF65" t="n">
         <v>1.33</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,133 +13409,133 @@
         </is>
       </c>
       <c r="P66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U66" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W66" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ66" t="n">
         <v>1.74</v>
       </c>
-      <c r="Q66" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R66" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U66" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W66" t="n">
+      <c r="AR66" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD66" t="n">
         <v>3.25</v>
       </c>
-      <c r="X66" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE66" t="n">
+      <c r="BE66" t="n">
         <v>1.53</v>
       </c>
-      <c r="AF66" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF66" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,79 +13606,79 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
@@ -13720,19 +13720,19 @@
         <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BE67" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,133 +13803,133 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM68" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV68" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW68" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY68" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AZ68" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BA68" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD68" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,133 +14394,133 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR71" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AW71" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX71" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AY71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AZ71" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA71" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,133 +14591,133 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO72" t="n">
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX72" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY72" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ72" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA72" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD72" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,133 +14788,133 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ73" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM73" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AO73" t="n">
         <v>0</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AT73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU73" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AV73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AW73" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AX73" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AY73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AZ73" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA73" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD73" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE73" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,133 +14985,133 @@
         </is>
       </c>
       <c r="P74" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W74" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ74" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q74" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R74" t="n">
-        <v>5</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T74" t="n">
-        <v>2</v>
-      </c>
-      <c r="U74" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="V74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W74" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="X74" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH74" t="n">
+      <c r="BA74" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB74" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI74" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP74" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ74" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR74" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS74" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT74" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU74" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW74" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX74" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY74" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ74" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA74" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BB74" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BC74" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="BD74" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="BE74" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="BF74" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="BG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,133 +15379,133 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.47</v>
+        <v>3.46</v>
       </c>
       <c r="R76" t="n">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="S76" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W76" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK76" t="n">
         <v>1.57</v>
       </c>
-      <c r="T76" t="n">
-        <v>3</v>
-      </c>
-      <c r="U76" t="n">
-        <v>7</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W76" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="X76" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y76" t="n">
+      <c r="AL76" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE76" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z76" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ76" t="n">
+      <c r="BF76" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV76" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BA76" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE76" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BF76" t="n">
-        <v>1.45</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,133 +15576,133 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.55</v>
+        <v>6.47</v>
       </c>
       <c r="R77" t="n">
-        <v>6.82</v>
+        <v>10.5</v>
       </c>
       <c r="S77" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="T77" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="V77" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="W77" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="X77" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="Z77" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AD77" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.43</v>
+        <v>1.92</v>
       </c>
       <c r="AI77" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AU77" t="n">
         <v>5.2</v>
       </c>
-      <c r="AJ77" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>4</v>
-      </c>
       <c r="AV77" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="AW77" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="AY77" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC77" t="n">
         <v>1.5</v>
       </c>
-      <c r="AZ77" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA77" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB77" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC77" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BD77" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE77" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="BF77" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="BG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,133 +15773,133 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="R78" t="n">
-        <v>2.42</v>
+        <v>6.82</v>
       </c>
       <c r="S78" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="T78" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U78" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="V78" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W78" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X78" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Y78" t="n">
         <v>1.47</v>
       </c>
       <c r="Z78" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC78" t="n">
         <v>1.2</v>
       </c>
       <c r="AD78" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AI78" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AJ78" t="n">
         <v>1.15</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AL78" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW78" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM78" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW78" t="n">
+      <c r="AX78" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE78" t="n">
         <v>1.85</v>
       </c>
-      <c r="AX78" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE78" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BF78" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,133 +15970,133 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.12</v>
+        <v>1.81</v>
       </c>
       <c r="Q79" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="R79" t="n">
-        <v>17</v>
+        <v>4.09</v>
       </c>
       <c r="S79" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.99</v>
+        <v>1.9</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AN79" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AU79" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AV79" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA79" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE79" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BG79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,133 +16167,133 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.81</v>
+        <v>1.12</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="R80" t="n">
-        <v>4.09</v>
+        <v>17</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.9</v>
+        <v>2.99</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
-        <v>1.77</v>
+        <v>4.69</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF81" t="n">
         <v>2</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R82" t="n">
-        <v>8</v>
+        <v>1.77</v>
       </c>
       <c r="S82" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AF82" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AG82" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R83" t="n">
+        <v>8</v>
+      </c>
+      <c r="S83" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="T83" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U83" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="V83" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W83" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X83" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN83" t="n">
         <v>3.7</v>
       </c>
-      <c r="R83" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN83" t="n">
-        <v>0</v>
-      </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q84" t="n">
-        <v>6.9</v>
+        <v>3.66</v>
       </c>
       <c r="R84" t="n">
-        <v>14</v>
+        <v>3.68</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.13</v>
+        <v>10.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.66</v>
+        <v>5.98</v>
       </c>
       <c r="R85" t="n">
-        <v>3.68</v>
+        <v>1.33</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>10.4</v>
+        <v>1.12</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="R86" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
       <c r="R92" t="n">
-        <v>4.11</v>
+        <v>4.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.63</v>
+        <v>2.39</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.42</v>
+        <v>3.58</v>
       </c>
       <c r="R96" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,16 +19364,16 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q101" t="n">
         <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>

--- a/jogos_2026-04-22.xlsx
+++ b/jogos_2026-04-22.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,64 +801,64 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
         <v>2.2</v>
       </c>
       <c r="U2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X2" t="n">
         <v>2.63</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.71</v>
-      </c>
       <c r="Y2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF2" t="n">
         <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.11</v>
@@ -873,7 +873,7 @@
         <v>1.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>3.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF2" t="n">
         <v>1.18</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,64 +998,64 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
         <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.25</v>
+        <v>6.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF3" t="n">
         <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.57</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.11</v>
@@ -1070,7 +1070,7 @@
         <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>3.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BF3" t="n">
         <v>1.18</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="R18" t="n">
-        <v>3.03</v>
+        <v>3.79</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="X18" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="AH18" t="n">
         <v>1.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="R23" t="n">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="U23" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="X23" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="R25" t="n">
-        <v>2.07</v>
+        <v>3.24</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>2.51</v>
+        <v>4.45</v>
       </c>
       <c r="V25" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="X25" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.04</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK25" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>4.17</v>
+        <v>2.07</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>3.24</v>
+        <v>4.17</v>
       </c>
       <c r="S27" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6129,13 +6129,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6144,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6159,40 +6159,40 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,19 +6326,19 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+      